--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,24 @@
   </si>
   <si>
     <t>CastConfigCategory</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>cn.etetet.twsmmo.ActionConfigCategory</t>
+  </si>
+  <si>
+    <t>ActionConfig</t>
+  </si>
+  <si>
+    <t>ActionConfigCategory</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>Bullet</t>
   </si>
 </sst>
 </file>
@@ -1079,8 +1097,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="3" width="29.375" customWidth="1"/>
@@ -1205,22 +1223,22 @@
         <v>30</v>
       </c>
       <c r="D4" t="str">
-        <f>_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
+        <f t="shared" ref="D4:D8" si="0">_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
         <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
       </c>
       <c r="E4" t="str">
-        <f>_xlfn.CONCAT(C4,"Config")</f>
+        <f t="shared" ref="E4:E8" si="1">_xlfn.CONCAT(C4,"Config")</f>
         <v>DemoConfig</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <f t="shared" ref="G4:G8" si="2">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
       </c>
       <c r="M4" t="str">
-        <f>_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <f t="shared" ref="M4:M8" si="3">_xlfn.CONCAT(C4,"ConfigCategory")</f>
         <v>DemoConfigCategory</v>
       </c>
     </row>
@@ -1241,11 +1259,89 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B5,"\Luban\Config\Datas\",C5,".xlsx")</f>
+        <f t="shared" si="2"/>
         <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Cast.xlsx</v>
       </c>
       <c r="M5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:13">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="2"/>
+        <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Action.xlsx</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:13">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>cn.etetet.twsmmo.BuffConfigCategory</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="1"/>
+        <v>BuffConfig</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="2"/>
+        <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Buff.xlsx</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="3"/>
+        <v>BuffConfigCategory</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="2:13">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>cn.etetet.twsmmo.BulletConfigCategory</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="1"/>
+        <v>BulletConfig</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="2"/>
+        <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Bullet.xlsx</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="3"/>
+        <v>BulletConfigCategory</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Bullet</t>
+  </si>
+  <si>
+    <t>ParticleEffect</t>
   </si>
 </sst>
 </file>
@@ -1097,8 +1100,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="3" width="29.375" customWidth="1"/>
@@ -1223,22 +1226,22 @@
         <v>30</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" ref="D4:D8" si="0">_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
+        <f t="shared" ref="D4:D9" si="0">_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
         <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4:E8" si="1">_xlfn.CONCAT(C4,"Config")</f>
+        <f t="shared" ref="E4:E9" si="1">_xlfn.CONCAT(C4,"Config")</f>
         <v>DemoConfig</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4:G8" si="2">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <f t="shared" ref="G4:G9" si="2">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
       </c>
       <c r="M4" t="str">
-        <f t="shared" ref="M4:M8" si="3">_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <f t="shared" ref="M4:M9" si="3">_xlfn.CONCAT(C4,"ConfigCategory")</f>
         <v>DemoConfigCategory</v>
       </c>
     </row>
@@ -1342,6 +1345,33 @@
       <c r="M8" t="str">
         <f t="shared" si="3"/>
         <v>BulletConfigCategory</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="2:13">
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>cn.etetet.twsmmo.ParticleEffectConfigCategory</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="1"/>
+        <v>ParticleEffectConfig</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="2"/>
+        <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\ParticleEffect.xlsx</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="3"/>
+        <v>ParticleEffectConfigCategory</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>Bullet</t>
-  </si>
-  <si>
-    <t>ParticleEffect</t>
   </si>
 </sst>
 </file>
@@ -1100,8 +1097,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="3" width="29.375" customWidth="1"/>
@@ -1226,22 +1223,22 @@
         <v>30</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" ref="D4:D9" si="0">_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
+        <f>_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
         <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4:E9" si="1">_xlfn.CONCAT(C4,"Config")</f>
+        <f>_xlfn.CONCAT(C4,"Config")</f>
         <v>DemoConfig</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4:G9" si="2">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
       </c>
       <c r="M4" t="str">
-        <f t="shared" ref="M4:M9" si="3">_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <f>_xlfn.CONCAT(C4,"ConfigCategory")</f>
         <v>DemoConfigCategory</v>
       </c>
     </row>
@@ -1262,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B5,"\Luban\Config\Datas\",C5,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Cast.xlsx</v>
       </c>
       <c r="M5" t="s">
@@ -1286,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B6,"\Luban\Config\Datas\",C6,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Action.xlsx</v>
       </c>
       <c r="M6" t="s">
@@ -1301,22 +1298,22 @@
         <v>40</v>
       </c>
       <c r="D7" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT("cn.etetet.",B7,".",C7,"ConfigCategory")</f>
         <v>cn.etetet.twsmmo.BuffConfigCategory</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(C7,"Config")</f>
         <v>BuffConfig</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B7,"\Luban\Config\Datas\",C7,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Buff.xlsx</v>
       </c>
       <c r="M7" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.CONCAT(C7,"ConfigCategory")</f>
         <v>BuffConfigCategory</v>
       </c>
     </row>
@@ -1328,50 +1325,23 @@
         <v>41</v>
       </c>
       <c r="D8" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT("cn.etetet.",B8,".",C8,"ConfigCategory")</f>
         <v>cn.etetet.twsmmo.BulletConfigCategory</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(C8,"Config")</f>
         <v>BulletConfig</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B8,"\Luban\Config\Datas\",C8,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\Bullet.xlsx</v>
       </c>
       <c r="M8" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.CONCAT(C8,"ConfigCategory")</f>
         <v>BulletConfigCategory</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="2:13">
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="str">
-        <f t="shared" si="0"/>
-        <v>cn.etetet.twsmmo.ParticleEffectConfigCategory</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="1"/>
-        <v>ParticleEffectConfig</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="2"/>
-        <v>..\..\..\..\cn.etetet.twsmmo\Luban\Config\Datas\ParticleEffect.xlsx</v>
-      </c>
-      <c r="M9" t="str">
-        <f t="shared" si="3"/>
-        <v>ParticleEffectConfigCategory</v>
       </c>
     </row>
   </sheetData>
